--- a/inst/ems_template_new/upload-test-3D_loc.xlsx
+++ b/inst/ems_template_new/upload-test-3D_loc.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>B01-R</t>
   </si>
@@ -85,22 +85,97 @@
     <t xml:space="preserve">Provider</t>
   </si>
   <si>
+    <t xml:space="preserve">GSOD_600600-99999 (SIDI IFNI - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD Weather Station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gsod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601550-99999 (ANFA - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601950-99999 (MIDELT - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602520-99999 (AL MASSIRA - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_603400-99999 (NADOR-AROUI - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601560-99999 (MOHAMMED V - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601010-99999 (TANGER IBN BATOUTA INTL - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601270-99999 (TAZA - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602650-99999 (OUARZAZATE - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601050-99999 (LARACHE - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601060-99999 (CHEFCHAOUEN - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601350-99999 (RABAT SALE INTL - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601070-99999 (CHERIF EL IDRISSI - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601360-99999 (SIDI SLIMANE - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602100-99999 (MOULAY ALI CHERIF - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602800-99999 (GUELMIN - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601150-99999 (ANGADS - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602200-99999 (ESSAOUIRA / MOGADOR INTL - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602850-99999 (PLAGE BLANCHE - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601410-99999 (SAISS - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601850-99999 (SAFI - MA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GSOD_601900-99999 (KASBA-TADLA - MA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSOD Weather Station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gsod</t>
-  </si>
-  <si>
     <t xml:space="preserve">GSOD_602300-99999 (MENARA - MA)</t>
   </si>
   <si>
     <t xml:space="preserve">GSOD_603180-99999 (SANIAT RMEL - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601500-99999 (BASSATINE - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_601910-99999 (BENI-MELLAL - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_602500-99999 (INEZGANE - MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSOD_603380-99999 (MELILLA - MA)</t>
   </si>
 </sst>
 </file>
@@ -513,10 +588,10 @@
         <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>-6.283</v>
+        <v>-10.18</v>
       </c>
       <c r="C2" t="n">
-        <v>32.533</v>
+        <v>29.369</v>
       </c>
       <c r="D2"/>
       <c r="E2" s="3" t="n">
@@ -537,10 +612,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-8.036</v>
+        <v>-7.66</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>31.607</v>
+        <v>33.557</v>
       </c>
       <c r="D3"/>
       <c r="E3" s="3" t="n">
@@ -561,10 +636,10 @@
         <v>27</v>
       </c>
       <c r="B4" t="n">
-        <v>-5.32</v>
+        <v>-4.733</v>
       </c>
       <c r="C4" t="n">
-        <v>35.594</v>
+        <v>32.683</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
@@ -577,6 +652,606 @@
         <v>24</v>
       </c>
       <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-9.413</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30.325</v>
+      </c>
+      <c r="D5"/>
+      <c r="E5" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-3.017</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34.983</v>
+      </c>
+      <c r="D6"/>
+      <c r="E6" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-7.59</v>
+      </c>
+      <c r="C7" t="n">
+        <v>33.367</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-5.917</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.727</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34.217</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-6.909</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30.939</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>35.167</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-6.752</v>
+      </c>
+      <c r="C13" t="n">
+        <v>34.051</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="C14" t="n">
+        <v>35.177</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="C15" t="n">
+        <v>34.233</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-4.398</v>
+      </c>
+      <c r="C16" t="n">
+        <v>31.948</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-10.067</v>
+      </c>
+      <c r="C17" t="n">
+        <v>29.017</v>
+      </c>
+      <c r="D17"/>
+      <c r="E17" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.924</v>
+      </c>
+      <c r="C18" t="n">
+        <v>34.787</v>
+      </c>
+      <c r="D18"/>
+      <c r="E18" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-9.683</v>
+      </c>
+      <c r="C19" t="n">
+        <v>31.399</v>
+      </c>
+      <c r="D19"/>
+      <c r="E19" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-11.161</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28.448</v>
+      </c>
+      <c r="D20"/>
+      <c r="E20" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-4.978</v>
+      </c>
+      <c r="C21" t="n">
+        <v>33.927</v>
+      </c>
+      <c r="D21"/>
+      <c r="E21" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-9.233</v>
+      </c>
+      <c r="C22" t="n">
+        <v>32.283</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-6.283</v>
+      </c>
+      <c r="C23" t="n">
+        <v>32.533</v>
+      </c>
+      <c r="D23"/>
+      <c r="E23" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-8.036</v>
+      </c>
+      <c r="C24" t="n">
+        <v>31.607</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="C25" t="n">
+        <v>35.594</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-5.515</v>
+      </c>
+      <c r="C26" t="n">
+        <v>33.879</v>
+      </c>
+      <c r="D26"/>
+      <c r="E26" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32.367</v>
+      </c>
+      <c r="D27"/>
+      <c r="E27" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F27" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-9.546</v>
+      </c>
+      <c r="C28" t="n">
+        <v>30.381</v>
+      </c>
+      <c r="D28"/>
+      <c r="E28" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-2.956</v>
+      </c>
+      <c r="C29" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="D29"/>
+      <c r="E29" t="n">
+        <v>4326</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" t="s">
         <v>25</v>
       </c>
     </row>
